--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>119984264</v>
       </c>
       <c r="B3" t="n">
-        <v>56233</v>
+        <v>56243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>105073304</v>
       </c>
       <c r="B2" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688821.8371628782</v>
+        <v>688822</v>
       </c>
       <c r="R2" t="n">
-        <v>6376136.124116917</v>
+        <v>6376136</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2003-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2003-01-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105073304</v>
       </c>
       <c r="B2" t="n">
-        <v>97660</v>
+        <v>97666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105073304</v>
       </c>
       <c r="B2" t="n">
-        <v>97666</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105073304</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105073304</v>
       </c>
       <c r="B2" t="n">
-        <v>97669</v>
+        <v>97696</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105073304</v>
       </c>
       <c r="B2" t="n">
-        <v>97696</v>
+        <v>97702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105073304</v>
       </c>
       <c r="B2" t="n">
-        <v>97702</v>
+        <v>97709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105073304</v>
       </c>
       <c r="B2" t="n">
-        <v>97709</v>
+        <v>97713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105073304</v>
       </c>
       <c r="B2" t="n">
-        <v>97713</v>
+        <v>97720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105073304</v>
       </c>
       <c r="B2" t="n">
-        <v>97723</v>
+        <v>97728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105073304</v>
       </c>
       <c r="B2" t="n">
-        <v>97728</v>
+        <v>97736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,590 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129511961</v>
+      </c>
+      <c r="B4" t="n">
+        <v>86829</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tofta Krokstäde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>688779</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6376244</v>
+      </c>
+      <c r="S4" t="n">
+        <v>93</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tofta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I kalkbarrskog med tall och gran.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129512394</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98694</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tofta Krokstäde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>688779</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6376244</v>
+      </c>
+      <c r="S5" t="n">
+        <v>93</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tofta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I kalkbarrskog med tall och gran på fuktigare mark.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129512177</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96312</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tofta Krokstäde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>688779</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6376244</v>
+      </c>
+      <c r="S6" t="n">
+        <v>93</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tofta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I kalkbarrskog med tall och gran.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129512161</v>
+      </c>
+      <c r="B7" t="n">
+        <v>95952</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tofta Krokstäde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>688779</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6376244</v>
+      </c>
+      <c r="S7" t="n">
+        <v>93</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tofta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I kalkbarrskog med tall och gran.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129511954</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101810</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tofta Krokstäde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>688779</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6376244</v>
+      </c>
+      <c r="S8" t="n">
+        <v>93</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tofta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>129511961</v>
       </c>
       <c r="B4" t="n">
-        <v>86829</v>
+        <v>86830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>129512394</v>
       </c>
       <c r="B5" t="n">
-        <v>98694</v>
+        <v>98702</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>129512177</v>
       </c>
       <c r="B6" t="n">
-        <v>96312</v>
+        <v>96320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129512161</v>
       </c>
       <c r="B7" t="n">
-        <v>95952</v>
+        <v>95960</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>129511954</v>
       </c>
       <c r="B8" t="n">
-        <v>101810</v>
+        <v>101820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>129512394</v>
       </c>
       <c r="B5" t="n">
-        <v>98702</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>129512177</v>
       </c>
       <c r="B6" t="n">
-        <v>96320</v>
+        <v>96323</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129512161</v>
       </c>
       <c r="B7" t="n">
-        <v>95960</v>
+        <v>95963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>129511954</v>
       </c>
       <c r="B8" t="n">
-        <v>101820</v>
+        <v>101823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>129511961</v>
       </c>
       <c r="B4" t="n">
-        <v>86830</v>
+        <v>86858</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>129512394</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>129512177</v>
       </c>
       <c r="B6" t="n">
-        <v>96323</v>
+        <v>96352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129512161</v>
       </c>
       <c r="B7" t="n">
-        <v>95963</v>
+        <v>95992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>129511954</v>
       </c>
       <c r="B8" t="n">
-        <v>101823</v>
+        <v>101852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>129511961</v>
       </c>
       <c r="B4" t="n">
-        <v>86858</v>
+        <v>86864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>129512394</v>
       </c>
       <c r="B5" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>129512177</v>
       </c>
       <c r="B6" t="n">
-        <v>96352</v>
+        <v>96364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129512161</v>
       </c>
       <c r="B7" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>129511954</v>
       </c>
       <c r="B8" t="n">
-        <v>101852</v>
+        <v>101864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>129511961</v>
       </c>
       <c r="B4" t="n">
-        <v>86864</v>
+        <v>86865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>129512394</v>
       </c>
       <c r="B5" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>129512177</v>
       </c>
       <c r="B6" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129512161</v>
       </c>
       <c r="B7" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>129511954</v>
       </c>
       <c r="B8" t="n">
-        <v>101864</v>
+        <v>101865</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>129511961</v>
       </c>
       <c r="B4" t="n">
-        <v>86865</v>
+        <v>86870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>129512394</v>
       </c>
       <c r="B5" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>129512177</v>
       </c>
       <c r="B6" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129512161</v>
       </c>
       <c r="B7" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>129511954</v>
       </c>
       <c r="B8" t="n">
-        <v>101865</v>
+        <v>101870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>129511961</v>
       </c>
       <c r="B4" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>129512394</v>
       </c>
       <c r="B5" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>129512177</v>
       </c>
       <c r="B6" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129512161</v>
       </c>
       <c r="B7" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>129511954</v>
       </c>
       <c r="B8" t="n">
-        <v>101870</v>
+        <v>101874</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>129511961</v>
       </c>
       <c r="B4" t="n">
-        <v>86874</v>
+        <v>86876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>129512394</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>129512177</v>
       </c>
       <c r="B6" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129512161</v>
       </c>
       <c r="B7" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>129511954</v>
       </c>
       <c r="B8" t="n">
-        <v>101874</v>
+        <v>101876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>129512394</v>
       </c>
       <c r="B5" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>129512177</v>
       </c>
       <c r="B6" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129512161</v>
       </c>
       <c r="B7" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>129511954</v>
       </c>
       <c r="B8" t="n">
-        <v>101876</v>
+        <v>101886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105073304</v>
+        <v>129512177</v>
       </c>
       <c r="B2" t="n">
-        <v>97736</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Krokstäde 600 m SO, Gtl</t>
+          <t>Tofta Krokstäde, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688822</v>
+        <v>688779</v>
       </c>
       <c r="R2" t="n">
-        <v>6376136</v>
+        <v>6376244</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +744,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-01-31</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Mindre bestånd.</t>
+          <t>I kalkbarrskog med tall och gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,94 +773,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog på sand.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sebastian Bolander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119984264</v>
+        <v>129512161</v>
       </c>
       <c r="B3" t="n">
-        <v>56243</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100053</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krokstäde, Gtl</t>
+          <t>Tofta Krokstäde, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688598</v>
+        <v>688779</v>
       </c>
       <c r="R3" t="n">
-        <v>6376352</v>
+        <v>6376244</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +861,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I kalkbarrskog med tall och gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,36 +890,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Nilsson</t>
+          <t>Sebastian Bolander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Nilsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>129511961</v>
       </c>
       <c r="B4" t="n">
-        <v>86876</v>
+        <v>87170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1032,52 +1025,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129512394</v>
+        <v>119984264</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>56845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>100053</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tofta Krokstäde, Gtl</t>
+          <t>Krokstäde, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>688779</v>
+        <v>688598</v>
       </c>
       <c r="R5" t="n">
-        <v>6376244</v>
+        <v>6376352</v>
       </c>
       <c r="S5" t="n">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,27 +1104,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I kalkbarrskog med tall och gran på fuktigare mark.</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,29 +1128,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Bolander</t>
+          <t>Johan Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Bolander</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Johan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129512177</v>
+        <v>129512394</v>
       </c>
       <c r="B6" t="n">
-        <v>96386</v>
+        <v>99096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,21 +1161,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1238,7 +1239,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I kalkbarrskog med tall och gran.</t>
+          <t>I kalkbarrskog med tall och gran på fuktigare mark.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129512161</v>
+        <v>105073304</v>
       </c>
       <c r="B7" t="n">
-        <v>96026</v>
+        <v>98194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,41 +1278,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>220686</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tofta Krokstäde, Gtl</t>
+          <t>Krokstäde 600 m SO, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688779</v>
+        <v>688822</v>
       </c>
       <c r="R7" t="n">
-        <v>6376244</v>
+        <v>6376136</v>
       </c>
       <c r="S7" t="n">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,27 +1332,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2003-01-31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I kalkbarrskog med tall och gran.</t>
+          <t>Mindre bestånd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,33 +1351,41 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrskog på sand.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Bolander</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Bolander</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>129511954</v>
       </c>
       <c r="B8" t="n">
-        <v>101886</v>
+        <v>102240</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">

--- a/artfynd/A 51737-2021 artfynd.xlsx
+++ b/artfynd/A 51737-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512177</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512161</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511961</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119984264</t>
         </is>
       </c>
     </row>
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512394</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,6 +1403,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105073304</t>
         </is>
       </c>
     </row>
@@ -1492,8 +1527,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511954</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>